--- a/outputs/evaluation/decision/v2/CF_M01/run_3/CF_M01_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M01/run_3/CF_M01_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6667</v>
+        <v>0.8571</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5714</v>
+        <v>0.8571</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8452</v>
+        <v>0.8706</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.875</v>
+        <v>0.4444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8</v>
+        <v>0.6667</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9283</v>
+        <v>0.9519</v>
       </c>
     </row>
     <row r="8">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6667</v>
+        <v>0.8571</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5714</v>
+        <v>0.8571</v>
       </c>
     </row>
     <row r="9">
@@ -726,19 +726,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -755,31 +755,31 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
         <v>4</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11</v>
+      </c>
+      <c r="K3" t="n">
         <v>4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>7</v>
-      </c>
-      <c r="K3" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -792,28 +792,28 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
@@ -829,22 +829,22 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,28 +974,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD07</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8136</v>
+        <v>0.7971</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1003,84 +1003,84 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.766</v>
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>The business layer and the data layer are divided into several different services to improve the security, scalability, and availability of the system.</t>
+          <t>Kinesis Data Streams is used to transmit data in near real-time.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>C_02, C_04, Security</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_06, AU_07, AU_08, AU_09, AU_10</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>50</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+          <t>CF_M01_C01</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M01_P03</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>42</v>
-      </c>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_AD01</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8353</v>
+        <v>0.8325</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5</v>
+        <v>0.1667</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1088,72 +1088,74 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.9471000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform. It increases the security of the system by reducing the entry points to the outside, since the only way to interact with the microservices is through the Api Gateway.</t>
+          <t>The platform lacks an efficient storage system that allows saving all necessary data on a large scale and a system that allows us to obtain and analyze this data. The objective of this is to improve the security, scalability and availability of the system.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>C_05, Security</t>
+          <t>R_24, R_25, C_03, C_04</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_12, AU_16, AU_18, AU_19, AU_20, AU_21</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>10, 42</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
+          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>*CF_M01_C07</t>
+          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_P03</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M01_AD06</t>
+          <t>CF_M01_AD02</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8477</v>
+        <v>0.8398</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -1162,10 +1164,10 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1185,129 +1187,299 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>NestJS allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+          <t>This design pattern allows only one component to interact between users and the services provided by the platform. It increases the security of the system by reducing the gateways to the outside, since the only way to interact with the microservices is through the Api Gateway.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Maintainability</t>
+          <t>C_05, Security</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>*CF_M01_C11</t>
+          <t>*CF_M01_C07</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8477</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>NestJS allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>*CF_M01_C11</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CF_M01_AD04</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.8603</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>AWS was chosen over other cloud services for its low price and its previous use by the company.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>C_02, Scalability</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>*CF_M01_C09, *CF_M01_C10</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>CF_M01_AD05</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>0.8841</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="C7" t="n">
+        <v>0.9575</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>TypeScript was chosen because, thanks to its static typing, it allows for the detection of errors at compile time.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>TypeScript was chosen over JavaScript because it is the default language for NestJS and because thanks to its static typing it allows the detection of errors at compile time.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>Maintainability</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>*CF_M01_C11</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>CF_M01_AU34</t>
         </is>
       </c>
-      <c r="U5" t="n">
+      <c r="U7" t="n">
         <v>46</v>
       </c>
     </row>
@@ -1322,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1365,71 +1537,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AWS is used for infrastructure because it allows the creation of scalable and highly available applications.</t>
+          <t>Amazon Athena is a serverless service that makes it unnecessary to manage infrastructure when there is an increase in the data set and users. In addition, to obtain data quickly, Athena performs queries in parallel.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_02, C_04</t>
+          <t>C_01, Performance</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD07</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6994</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AD_03</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>The objective of these services is to form a data lake where all history is stored to be processed in the analytical module, allowing the system to grow in capacity when data volume increases and scale automatically as data increases.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>R_24, R_25, C_03, C_04</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>AU_12, AU_16, AU_18, AU_19</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>44, 45</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CF_M01_AD01</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0.7308</v>
+        <v>0.6716</v>
       </c>
     </row>
   </sheetData>
@@ -1443,7 +1580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1509,75 +1646,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6377</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CF_M01_AD04</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>*CF_M01_C09, *CF_M01_C10</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>46</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0.6629</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CF_M01_AD07</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CF_M01_C01</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0.6732</v>
+        <v>0.6279</v>
       </c>
     </row>
   </sheetData>
